--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>17.6835712116611</v>
+      </c>
+      <c r="C2">
         <v>17.33313088369268</v>
-      </c>
-      <c r="C2">
-        <v>17.6835712116611</v>
       </c>
       <c r="D2">
         <v>5.769298153404113</v>
       </c>
       <c r="E2">
-        <v>12.83776793144554</v>
+        <v>13.09732124783518</v>
       </c>
       <c r="F2">
         <v>74.06491082071928</v>
       </c>
       <c r="G2">
-        <v>13.09732124783518</v>
+        <v>12.83776793144554</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.8352285736091</v>
+      </c>
+      <c r="C3">
         <v>27.74173853316034</v>
-      </c>
-      <c r="C3">
-        <v>27.8352285736091</v>
       </c>
       <c r="D3">
         <v>3.604676753782669</v>
       </c>
       <c r="E3">
-        <v>17.83152033946113</v>
+        <v>17.8916128082805</v>
       </c>
       <c r="F3">
         <v>64.27686685225837</v>
       </c>
       <c r="G3">
-        <v>17.8916128082805</v>
+        <v>17.83152033946113</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.8840393192358</v>
+      </c>
+      <c r="C4">
         <v>27.94727849646083</v>
-      </c>
-      <c r="C4">
-        <v>27.8840393192358</v>
       </c>
       <c r="D4">
         <v>3.578165938864629</v>
       </c>
       <c r="E4">
-        <v>17.93431441651182</v>
+        <v>17.89373260143674</v>
       </c>
       <c r="F4">
         <v>64.17195298205145</v>
       </c>
       <c r="G4">
-        <v>17.89373260143674</v>
+        <v>17.93431441651182</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.51236990274697</v>
+      </c>
+      <c r="C5">
         <v>31.46586394325688</v>
-      </c>
-      <c r="C5">
-        <v>27.51236990274697</v>
       </c>
       <c r="D5">
         <v>3.17804717456137</v>
       </c>
       <c r="E5">
-        <v>19.79256102048326</v>
+        <v>17.30574635103643</v>
       </c>
       <c r="F5">
         <v>62.90169262848032</v>
       </c>
       <c r="G5">
-        <v>17.30574635103643</v>
+        <v>19.79256102048326</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.51845496909548</v>
+      </c>
+      <c r="C6">
         <v>29.95885897010939</v>
-      </c>
-      <c r="C6">
-        <v>30.51845496909548</v>
       </c>
       <c r="D6">
         <v>3.337910836316303</v>
       </c>
       <c r="E6">
-        <v>18.66859447900467</v>
+        <v>19.01730171073095</v>
       </c>
       <c r="F6">
         <v>62.31410381026438</v>
       </c>
       <c r="G6">
-        <v>19.01730171073095</v>
+        <v>18.66859447900467</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>22.57914046591735</v>
+      </c>
+      <c r="C7">
         <v>23.22679607818513</v>
-      </c>
-      <c r="C7">
-        <v>22.57914046591735</v>
       </c>
       <c r="D7">
         <v>4.305372108291817</v>
       </c>
       <c r="E7">
-        <v>15.92993853934036</v>
+        <v>15.48574838658078</v>
       </c>
       <c r="F7">
         <v>68.58431307407886</v>
       </c>
       <c r="G7">
-        <v>15.48574838658078</v>
+        <v>15.92993853934036</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>33.02946883884652</v>
+      </c>
+      <c r="C8">
         <v>20.82825638942792</v>
-      </c>
-      <c r="C8">
-        <v>33.02946883884652</v>
       </c>
       <c r="D8">
         <v>4.801170013000144</v>
       </c>
       <c r="E8">
-        <v>13.53734845522096</v>
+        <v>21.46754008603832</v>
       </c>
       <c r="F8">
         <v>64.99511145874071</v>
       </c>
       <c r="G8">
-        <v>21.46754008603833</v>
+        <v>13.53734845522096</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>23.47604446631588</v>
+      </c>
+      <c r="C9">
         <v>21.48111695751473</v>
-      </c>
-      <c r="C9">
-        <v>23.47604446631588</v>
       </c>
       <c r="D9">
         <v>4.655251409774436</v>
       </c>
       <c r="E9">
-        <v>14.81894150417827</v>
+        <v>16.19516016713092</v>
       </c>
       <c r="F9">
         <v>68.98589832869081</v>
       </c>
       <c r="G9">
-        <v>16.19516016713092</v>
+        <v>14.81894150417827</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.62732077517279</v>
+      </c>
+      <c r="C10">
         <v>31.03232145277138</v>
-      </c>
-      <c r="C10">
-        <v>24.62732077517279</v>
       </c>
       <c r="D10">
         <v>3.222446640100442</v>
       </c>
       <c r="E10">
-        <v>19.9360097508951</v>
+        <v>15.82126261032333</v>
       </c>
       <c r="F10">
         <v>64.24272763878157</v>
       </c>
       <c r="G10">
-        <v>15.82126261032333</v>
+        <v>19.9360097508951</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.74925053348193</v>
+      </c>
+      <c r="C11">
         <v>31.02532203301973</v>
-      </c>
-      <c r="C11">
-        <v>25.74925053348193</v>
       </c>
       <c r="D11">
         <v>3.2231736351865</v>
       </c>
       <c r="E11">
-        <v>19.78976662166258</v>
+        <v>16.42437935690078</v>
       </c>
       <c r="F11">
         <v>63.78585402143664</v>
       </c>
       <c r="G11">
-        <v>16.42437935690078</v>
+        <v>19.78976662166258</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.97344122834319</v>
+      </c>
+      <c r="C12">
         <v>30.68264342774147</v>
-      </c>
-      <c r="C12">
-        <v>28.97344122834319</v>
       </c>
       <c r="D12">
         <v>3.259171597633136</v>
       </c>
       <c r="E12">
-        <v>19.21796058937245</v>
+        <v>18.14740809331189</v>
       </c>
       <c r="F12">
         <v>62.63463131731566</v>
       </c>
       <c r="G12">
-        <v>18.14740809331189</v>
+        <v>19.21796058937245</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>33.07272806596571</v>
+      </c>
+      <c r="C13">
         <v>24.81567121853322</v>
-      </c>
-      <c r="C13">
-        <v>33.07272806596571</v>
       </c>
       <c r="D13">
         <v>4.029711673699016</v>
       </c>
       <c r="E13">
-        <v>15.71722262749519</v>
+        <v>20.94690187236112</v>
       </c>
       <c r="F13">
         <v>63.33587550014369</v>
       </c>
       <c r="G13">
-        <v>20.94690187236112</v>
+        <v>15.71722262749519</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.83908891750422</v>
+      </c>
+      <c r="C14">
         <v>33.87795374349884</v>
-      </c>
-      <c r="C14">
-        <v>25.83908891750422</v>
       </c>
       <c r="D14">
         <v>2.951772139401718</v>
       </c>
       <c r="E14">
-        <v>21.21123280212762</v>
+        <v>16.17804117018826</v>
       </c>
       <c r="F14">
         <v>62.61072602768412</v>
       </c>
       <c r="G14">
-        <v>16.17804117018826</v>
+        <v>21.21123280212762</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>24.33632747675368</v>
+      </c>
+      <c r="C15">
         <v>34.17327397729368</v>
-      </c>
-      <c r="C15">
-        <v>24.33632747675368</v>
       </c>
       <c r="D15">
         <v>2.926263373724293</v>
       </c>
       <c r="E15">
-        <v>21.55911923556295</v>
+        <v>15.35321977565434</v>
       </c>
       <c r="F15">
         <v>63.08766098878272</v>
       </c>
       <c r="G15">
-        <v>15.35321977565434</v>
+        <v>21.55911923556295</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>31.19547502636372</v>
+      </c>
+      <c r="C16">
         <v>19.29824561403509</v>
-      </c>
-      <c r="C16">
-        <v>31.19547502636372</v>
       </c>
       <c r="D16">
         <v>5.181818181818182</v>
       </c>
       <c r="E16">
+        <v>20.72875525544655</v>
+      </c>
+      <c r="F16">
+        <v>66.44795515352273</v>
+      </c>
+      <c r="G16">
         <v>12.8232895910307</v>
-      </c>
-      <c r="F16">
-        <v>66.44795515352274</v>
-      </c>
-      <c r="G16">
-        <v>20.72875525544655</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.82571534745448</v>
+      </c>
+      <c r="C17">
         <v>27.9271646228168</v>
-      </c>
-      <c r="C17">
-        <v>26.82571534745448</v>
       </c>
       <c r="D17">
         <v>3.580743027464339</v>
       </c>
       <c r="E17">
+        <v>17.33454999519738</v>
+      </c>
+      <c r="F17">
+        <v>64.61915281913362</v>
+      </c>
+      <c r="G17">
         <v>18.046297185669</v>
-      </c>
-      <c r="F17">
-        <v>64.6191528191336</v>
-      </c>
-      <c r="G17">
-        <v>17.33454999519738</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.93552759571991</v>
+      </c>
+      <c r="C18">
         <v>31.07368958203767</v>
-      </c>
-      <c r="C18">
-        <v>26.93552759571991</v>
       </c>
       <c r="D18">
         <v>3.218156625269424</v>
       </c>
       <c r="E18">
-        <v>19.66574490846335</v>
+        <v>17.04680782350685</v>
       </c>
       <c r="F18">
         <v>63.28744726802979</v>
       </c>
       <c r="G18">
-        <v>17.04680782350685</v>
+        <v>19.66574490846335</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>23.15847239891242</v>
+      </c>
+      <c r="C19">
         <v>31.0933173688543</v>
-      </c>
-      <c r="C19">
-        <v>23.15847239891242</v>
       </c>
       <c r="D19">
         <v>3.216125150421179</v>
       </c>
       <c r="E19">
-        <v>20.15750832821243</v>
+        <v>15.01342216759921</v>
       </c>
       <c r="F19">
         <v>64.82906950418837</v>
       </c>
       <c r="G19">
-        <v>15.01342216759921</v>
+        <v>20.15750832821243</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>27.07390047168</v>
+      </c>
+      <c r="C20">
         <v>24.5406510188229</v>
-      </c>
-      <c r="C20">
-        <v>27.07390047168</v>
       </c>
       <c r="D20">
         <v>4.074871523306334</v>
       </c>
       <c r="E20">
-        <v>16.186210873275</v>
+        <v>17.85705936898538</v>
       </c>
       <c r="F20">
         <v>65.95672975773964</v>
       </c>
       <c r="G20">
-        <v>17.85705936898538</v>
+        <v>16.186210873275</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>22.03196428955886</v>
+      </c>
+      <c r="C21">
         <v>30.66892488320188</v>
-      </c>
-      <c r="C21">
-        <v>22.03196428955886</v>
       </c>
       <c r="D21">
         <v>3.260629460629461</v>
       </c>
       <c r="E21">
-        <v>20.0843132278713</v>
+        <v>14.42818336482155</v>
       </c>
       <c r="F21">
         <v>65.48750340730714</v>
       </c>
       <c r="G21">
-        <v>14.42818336482155</v>
+        <v>20.0843132278713</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.26077296292378</v>
+      </c>
+      <c r="C22">
         <v>35.02516588322425</v>
-      </c>
-      <c r="C22">
-        <v>27.26077296292378</v>
       </c>
       <c r="D22">
         <v>2.855089975402408</v>
       </c>
       <c r="E22">
-        <v>21.58237869050945</v>
+        <v>16.79798826487846</v>
       </c>
       <c r="F22">
         <v>61.61963304461209</v>
       </c>
       <c r="G22">
-        <v>16.79798826487846</v>
+        <v>21.58237869050945</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.91301909716814</v>
+      </c>
+      <c r="C23">
         <v>24.20885385837565</v>
-      </c>
-      <c r="C23">
-        <v>27.91301909716814</v>
       </c>
       <c r="D23">
         <v>4.130720131775364</v>
       </c>
       <c r="E23">
-        <v>15.91411766633354</v>
+        <v>18.34911610990055</v>
       </c>
       <c r="F23">
         <v>65.73676622376591</v>
       </c>
       <c r="G23">
-        <v>18.34911610990055</v>
+        <v>15.91411766633354</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>18.08747507212144</v>
+      </c>
+      <c r="C24">
         <v>30.37038471219191</v>
-      </c>
-      <c r="C24">
-        <v>18.08747507212144</v>
       </c>
       <c r="D24">
         <v>3.292681371924008</v>
       </c>
       <c r="E24">
-        <v>20.45724271945955</v>
+        <v>12.18357525724794</v>
       </c>
       <c r="F24">
         <v>67.35918202329252</v>
       </c>
       <c r="G24">
-        <v>12.18357525724794</v>
+        <v>20.45724271945955</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.65899269804759</v>
+      </c>
+      <c r="C25">
         <v>22.46388153551961</v>
-      </c>
-      <c r="C25">
-        <v>29.65899269804759</v>
       </c>
       <c r="D25">
         <v>4.45159042714329</v>
       </c>
       <c r="E25">
-        <v>14.76693209269035</v>
+        <v>19.49673436521428</v>
       </c>
       <c r="F25">
-        <v>65.73633354209538</v>
+        <v>65.73633354209537</v>
       </c>
       <c r="G25">
-        <v>19.49673436521428</v>
+        <v>14.76693209269034</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.22893130403558</v>
+      </c>
+      <c r="C26">
         <v>14.83647763997459</v>
-      </c>
-      <c r="C26">
-        <v>29.22893130403558</v>
       </c>
       <c r="D26">
         <v>6.74014428671166</v>
       </c>
       <c r="E26">
-        <v>10.29843162819235</v>
+        <v>20.28865327095636</v>
       </c>
       <c r="F26">
         <v>69.41291510085129</v>
       </c>
       <c r="G26">
-        <v>20.28865327095636</v>
+        <v>10.29843162819235</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>23.81824972571722</v>
+      </c>
+      <c r="C27">
         <v>26.67662643852564</v>
-      </c>
-      <c r="C27">
-        <v>23.81824972571722</v>
       </c>
       <c r="D27">
         <v>3.7485999299965</v>
       </c>
       <c r="E27">
-        <v>17.72593666870894</v>
+        <v>15.82661837584632</v>
       </c>
       <c r="F27">
         <v>66.44744495544474</v>
       </c>
       <c r="G27">
-        <v>15.82661837584632</v>
+        <v>17.72593666870894</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>26.89106630316445</v>
+      </c>
+      <c r="C28">
         <v>27.55238840751838</v>
-      </c>
-      <c r="C28">
-        <v>26.89106630316445</v>
       </c>
       <c r="D28">
         <v>3.629449415452942</v>
       </c>
       <c r="E28">
-        <v>17.83979027090009</v>
+        <v>17.4115933585785</v>
       </c>
       <c r="F28">
         <v>64.7486163705214</v>
       </c>
       <c r="G28">
-        <v>17.4115933585785</v>
+        <v>17.83979027090009</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.74146157709693</v>
+      </c>
+      <c r="C29">
         <v>24.99372174786539</v>
-      </c>
-      <c r="C29">
-        <v>30.74146157709693</v>
       </c>
       <c r="D29">
         <v>4.001004772670183</v>
       </c>
       <c r="E29">
+        <v>19.73957388482393</v>
+      </c>
+      <c r="F29">
+        <v>64.21156598335045</v>
+      </c>
+      <c r="G29">
         <v>16.0488601318256</v>
-      </c>
-      <c r="F29">
-        <v>64.21156598335047</v>
-      </c>
-      <c r="G29">
-        <v>19.73957388482393</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.24872661493788</v>
+      </c>
+      <c r="C30">
         <v>32.854127989083</v>
-      </c>
-      <c r="C30">
-        <v>25.24872661493788</v>
       </c>
       <c r="D30">
         <v>3.043757546486356</v>
       </c>
       <c r="E30">
-        <v>20.78022441237279</v>
+        <v>15.96981071478753</v>
       </c>
       <c r="F30">
         <v>63.24996487283968</v>
       </c>
       <c r="G30">
-        <v>15.96981071478753</v>
+        <v>20.78022441237279</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>22.47259878857802</v>
+      </c>
+      <c r="C31">
         <v>25.01201807518508</v>
-      </c>
-      <c r="C31">
-        <v>22.47259878857802</v>
       </c>
       <c r="D31">
         <v>3.99807803190467</v>
       </c>
       <c r="E31">
-        <v>16.95906909280551</v>
+        <v>15.23724932569529</v>
       </c>
       <c r="F31">
         <v>67.80368158149919</v>
       </c>
       <c r="G31">
-        <v>15.23724932569529</v>
+        <v>16.95906909280551</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>27.73499875802846</v>
+      </c>
+      <c r="C32">
         <v>31.03509456726163</v>
-      </c>
-      <c r="C32">
-        <v>27.73499875802846</v>
       </c>
       <c r="D32">
         <v>3.222158701120512</v>
       </c>
       <c r="E32">
+        <v>17.46865431464139</v>
+      </c>
+      <c r="F32">
+        <v>62.98415394586863</v>
+      </c>
+      <c r="G32">
         <v>19.54719173948997</v>
-      </c>
-      <c r="F32">
-        <v>62.98415394586862</v>
-      </c>
-      <c r="G32">
-        <v>17.46865431464139</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>30.08836658467705</v>
+      </c>
+      <c r="C33">
         <v>35.95335701922201</v>
-      </c>
-      <c r="C33">
-        <v>30.08836658467705</v>
       </c>
       <c r="D33">
         <v>2.781381442254092</v>
       </c>
       <c r="E33">
-        <v>21.65320633805908</v>
+        <v>18.12096738796471</v>
       </c>
       <c r="F33">
         <v>60.2258262739762</v>
       </c>
       <c r="G33">
-        <v>18.12096738796471</v>
+        <v>21.65320633805908</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>28.72282781921336</v>
+      </c>
+      <c r="C34">
         <v>21.31143622107477</v>
-      </c>
-      <c r="C34">
-        <v>28.72282781921336</v>
       </c>
       <c r="D34">
         <v>4.692316320807628</v>
       </c>
       <c r="E34">
+        <v>19.1441788333767</v>
+      </c>
+      <c r="F34">
+        <v>66.65144168211293</v>
+      </c>
+      <c r="G34">
         <v>14.20437948451035</v>
-      </c>
-      <c r="F34">
-        <v>66.65144168211295</v>
-      </c>
-      <c r="G34">
-        <v>19.14417883337671</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>21.30685458039718</v>
+      </c>
+      <c r="C35">
         <v>23.09630578688875</v>
-      </c>
-      <c r="C35">
-        <v>21.30685458039718</v>
       </c>
       <c r="D35">
         <v>4.32969674556213</v>
       </c>
       <c r="E35">
-        <v>15.99432154264758</v>
+        <v>14.75511652667692</v>
       </c>
       <c r="F35">
         <v>69.2505619306755</v>
       </c>
       <c r="G35">
-        <v>14.75511652667692</v>
+        <v>15.99432154264758</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>26.75511817942184</v>
+      </c>
+      <c r="C36">
         <v>30.10280291714261</v>
-      </c>
-      <c r="C36">
-        <v>26.75511817942184</v>
       </c>
       <c r="D36">
         <v>3.321949795680093</v>
       </c>
       <c r="E36">
-        <v>19.19112704458884</v>
+        <v>17.05691239076854</v>
       </c>
       <c r="F36">
         <v>63.75196056464262</v>
       </c>
       <c r="G36">
-        <v>17.05691239076854</v>
+        <v>19.19112704458884</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>37.31278173622219</v>
+      </c>
+      <c r="C37">
         <v>15.48640395521303</v>
-      </c>
-      <c r="C37">
-        <v>37.31278173622219</v>
       </c>
       <c r="D37">
         <v>6.457276995305165</v>
       </c>
       <c r="E37">
-        <v>10.13513513513513</v>
+        <v>24.41948991244766</v>
       </c>
       <c r="F37">
-        <v>65.4453749524172</v>
+        <v>65.44537495241721</v>
       </c>
       <c r="G37">
-        <v>24.41948991244766</v>
+        <v>10.13513513513514</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>36.82957355230624</v>
+      </c>
+      <c r="C38">
         <v>14.97451082145365</v>
-      </c>
-      <c r="C38">
-        <v>36.82957355230624</v>
       </c>
       <c r="D38">
         <v>6.678014473550097</v>
       </c>
       <c r="E38">
-        <v>9.864366221257001</v>
+        <v>24.26125338079008</v>
       </c>
       <c r="F38">
         <v>65.87438039795293</v>
       </c>
       <c r="G38">
-        <v>24.26125338079008</v>
+        <v>9.864366221257001</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>31.81216931216931</v>
+      </c>
+      <c r="C39">
         <v>25.24801587301587</v>
-      </c>
-      <c r="C39">
-        <v>31.81216931216931</v>
       </c>
       <c r="D39">
         <v>3.960707269155206</v>
       </c>
       <c r="E39">
-        <v>16.07537635540583</v>
+        <v>20.25476365933256</v>
       </c>
       <c r="F39">
         <v>63.6698599852616</v>
       </c>
       <c r="G39">
-        <v>20.25476365933256</v>
+        <v>16.07537635540583</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>30.88788794965138</v>
+      </c>
+      <c r="C40">
         <v>22.12058575512638</v>
-      </c>
-      <c r="C40">
-        <v>30.88788794965138</v>
       </c>
       <c r="D40">
         <v>4.520675948955161</v>
       </c>
       <c r="E40">
-        <v>14.45709849887592</v>
+        <v>20.18704402557993</v>
       </c>
       <c r="F40">
         <v>65.35585747554414</v>
       </c>
       <c r="G40">
-        <v>20.18704402557993</v>
+        <v>14.45709849887592</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>30.47035382200217</v>
+      </c>
+      <c r="C41">
         <v>20.90629151068712</v>
-      </c>
-      <c r="C41">
-        <v>30.47035382200217</v>
       </c>
       <c r="D41">
         <v>4.783249097472924</v>
       </c>
       <c r="E41">
-        <v>13.81077739220613</v>
+        <v>20.12883411112441</v>
       </c>
       <c r="F41">
         <v>66.06038849666946</v>
       </c>
       <c r="G41">
-        <v>20.12883411112441</v>
+        <v>13.81077739220613</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>16.38701930672734</v>
+      </c>
+      <c r="C42">
         <v>20.36527948936708</v>
-      </c>
-      <c r="C42">
-        <v>16.38701930672734</v>
       </c>
       <c r="D42">
         <v>4.910318076027929</v>
       </c>
       <c r="E42">
-        <v>14.89209298026711</v>
+        <v>11.98299366883867</v>
       </c>
       <c r="F42">
         <v>73.12491335089422</v>
       </c>
       <c r="G42">
-        <v>11.98299366883867</v>
+        <v>14.89209298026711</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>30.7510053255081</v>
+      </c>
+      <c r="C43">
         <v>23.50179328333877</v>
-      </c>
-      <c r="C43">
-        <v>30.7510053255081</v>
       </c>
       <c r="D43">
         <v>4.254994450610432</v>
       </c>
       <c r="E43">
-        <v>15.2358942562426</v>
+        <v>19.93546023335776</v>
       </c>
       <c r="F43">
         <v>64.82864551039964</v>
       </c>
       <c r="G43">
-        <v>19.93546023335776</v>
+        <v>15.2358942562426</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>28.44731304153588</v>
+      </c>
+      <c r="C44">
         <v>26.42753853207773</v>
-      </c>
-      <c r="C44">
-        <v>28.44731304153588</v>
       </c>
       <c r="D44">
         <v>3.783931669558255</v>
       </c>
       <c r="E44">
-        <v>17.0638023304361</v>
+        <v>18.36793562834478</v>
       </c>
       <c r="F44">
         <v>64.56826204121911</v>
       </c>
       <c r="G44">
-        <v>18.36793562834478</v>
+        <v>17.0638023304361</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>31.64878048780488</v>
+      </c>
+      <c r="C45">
         <v>24.35121951219512</v>
-      </c>
-      <c r="C45">
-        <v>31.64878048780488</v>
       </c>
       <c r="D45">
         <v>4.106570512820513</v>
       </c>
       <c r="E45">
-        <v>15.60975609756098</v>
+        <v>20.28767979987492</v>
       </c>
       <c r="F45">
         <v>64.1025641025641</v>
       </c>
       <c r="G45">
-        <v>20.28767979987492</v>
+        <v>15.60975609756098</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>30.74447441904492</v>
+      </c>
+      <c r="C46">
         <v>28.67622698660609</v>
-      </c>
-      <c r="C46">
-        <v>30.74447441904492</v>
       </c>
       <c r="D46">
         <v>3.48720911041426</v>
       </c>
       <c r="E46">
-        <v>17.98776867355421</v>
+        <v>19.28512053200333</v>
       </c>
       <c r="F46">
         <v>62.72711079444247</v>
       </c>
       <c r="G46">
-        <v>19.28512053200333</v>
+        <v>17.98776867355421</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>29.56828382132935</v>
+      </c>
+      <c r="C47">
         <v>30.50865569566147</v>
-      </c>
-      <c r="C47">
-        <v>29.56828382132935</v>
       </c>
       <c r="D47">
         <v>3.277758318739054</v>
       </c>
       <c r="E47">
-        <v>19.05874499332443</v>
+        <v>18.47129506008011</v>
       </c>
       <c r="F47">
         <v>62.46995994659546</v>
       </c>
       <c r="G47">
-        <v>18.47129506008011</v>
+        <v>19.05874499332443</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>35.54169914263446</v>
+      </c>
+      <c r="C48">
         <v>37.41231488698363</v>
-      </c>
-      <c r="C48">
-        <v>35.54169914263446</v>
       </c>
       <c r="D48">
         <v>2.672916666666667</v>
       </c>
       <c r="E48">
-        <v>21.63136547994592</v>
+        <v>20.54979720594863</v>
       </c>
       <c r="F48">
         <v>57.81883731410545</v>
       </c>
       <c r="G48">
-        <v>20.54979720594863</v>
+        <v>21.63136547994592</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>28.88692941803716</v>
+      </c>
+      <c r="C49">
         <v>23.87934216462289</v>
-      </c>
-      <c r="C49">
-        <v>28.88692941803716</v>
       </c>
       <c r="D49">
         <v>4.187720051524259</v>
       </c>
       <c r="E49">
+        <v>18.90923246261645</v>
+      </c>
+      <c r="F49">
+        <v>65.45947542215899</v>
+      </c>
+      <c r="G49">
         <v>15.63129211522457</v>
-      </c>
-      <c r="F49">
-        <v>65.45947542215897</v>
-      </c>
-      <c r="G49">
-        <v>18.90923246261644</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>32.41947691531411</v>
+      </c>
+      <c r="C50">
         <v>24.87595660583635</v>
-      </c>
-      <c r="C50">
-        <v>32.41947691531411</v>
       </c>
       <c r="D50">
         <v>4.019945909398242</v>
       </c>
       <c r="E50">
-        <v>15.8147989734816</v>
+        <v>20.61056458511549</v>
       </c>
       <c r="F50">
-        <v>63.5746364414029</v>
+        <v>63.57463644140291</v>
       </c>
       <c r="G50">
-        <v>20.61056458511548</v>
+        <v>15.81479897348161</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>29.27029007370372</v>
+      </c>
+      <c r="C51">
         <v>24.9687513469247</v>
-      </c>
-      <c r="C51">
-        <v>29.27029007370372</v>
       </c>
       <c r="D51">
         <v>4.005006041774555</v>
       </c>
       <c r="E51">
-        <v>16.18834707279586</v>
+        <v>18.97722509431325</v>
       </c>
       <c r="F51">
         <v>64.83442783289087</v>
       </c>
       <c r="G51">
-        <v>18.97722509431325</v>
+        <v>16.18834707279586</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>30.91687712748436</v>
+      </c>
+      <c r="C52">
         <v>20.70275612166465</v>
-      </c>
-      <c r="C52">
-        <v>30.91687712748436</v>
       </c>
       <c r="D52">
         <v>4.830274742760157</v>
       </c>
       <c r="E52">
-        <v>13.65440324449595</v>
+        <v>20.39107763615295</v>
       </c>
       <c r="F52">
-        <v>65.9545191193511</v>
+        <v>65.95451911935109</v>
       </c>
       <c r="G52">
-        <v>20.39107763615296</v>
+        <v>13.65440324449594</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>30.26758035568608</v>
+      </c>
+      <c r="C53">
         <v>23.7493881546745</v>
-      </c>
-      <c r="C53">
-        <v>30.26758035568608</v>
       </c>
       <c r="D53">
         <v>4.210634789777411</v>
       </c>
       <c r="E53">
-        <v>15.41998156721082</v>
+        <v>19.65210758816487</v>
       </c>
       <c r="F53">
         <v>64.92791084462429</v>
       </c>
       <c r="G53">
-        <v>19.65210758816487</v>
+        <v>15.41998156721082</v>
       </c>
     </row>
   </sheetData>
